--- a/all_nodes_inventory.xlsx
+++ b/all_nodes_inventory.xlsx
@@ -783,7 +783,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cluster3</t>
+          <t>ocp4-roi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cluster3</t>
+          <t>ocp4-roi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cluster3</t>
+          <t>ocp4-roi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cluster3</t>
+          <t>ocp4-roi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cluster3</t>
+          <t>ocp4-roi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
